--- a/TestData/TMTT0035971_VerifyOpportunityToEngagementConversionDefaultStartDateStatus.xlsx
+++ b/TestData/TMTT0035971_VerifyOpportunityToEngagementConversionDefaultStartDateStatus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A05460-BC33-44CD-A5EE-4891C3EEC58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1F4776-9266-49AE-A769-2DEA2594C212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
@@ -170,9 +170,6 @@
     <t>Techno Coatings, Inc.</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -309,6 +306,9 @@
   </si>
   <si>
     <t>Verbally Engaged</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -643,13 +643,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -657,9 +657,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -673,12 +673,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FBB8EB1-471A-4668-845A-6810E22F6BA4}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -686,7 +686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -702,17 +702,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -725,17 +725,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -749,17 +749,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="11" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -851,10 +851,10 @@
         <v>40</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -862,91 +862,91 @@
         <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" t="s">
         <v>42</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>43</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" t="s">
         <v>44</v>
       </c>
-      <c r="G2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L2" t="s">
         <v>45</v>
       </c>
-      <c r="I2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K2" t="s">
-        <v>85</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>46</v>
-      </c>
-      <c r="M2" t="s">
-        <v>47</v>
       </c>
       <c r="N2" t="s">
         <v>0</v>
       </c>
       <c r="O2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" t="s">
         <v>48</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="S2" t="s">
         <v>48</v>
       </c>
-      <c r="Q2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="T2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="S2" t="s">
-        <v>49</v>
-      </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" t="s">
         <v>50</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>51</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>52</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>53</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>54</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>55</v>
       </c>
-      <c r="Z2" t="s">
-        <v>56</v>
-      </c>
       <c r="AA2" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AC2" t="s">
         <v>0</v>
       </c>
       <c r="AD2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AE2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -958,68 +958,68 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>65</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>67</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1030,13 +1030,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2386AE-B180-4489-BA71-14068DFEFD5A}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -1044,144 +1044,144 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" t="s">
         <v>70</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="C14">
         <v>13</v>

--- a/TestData/TMTT0035971_VerifyOpportunityToEngagementConversionDefaultStartDateStatus.xlsx
+++ b/TestData/TMTT0035971_VerifyOpportunityToEngagementConversionDefaultStartDateStatus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1F4776-9266-49AE-A769-2DEA2594C212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE15B2F-0943-46E8-8D52-6223263FD786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
@@ -643,13 +643,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -657,7 +657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -673,12 +673,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FBB8EB1-471A-4668-845A-6810E22F6BA4}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -686,7 +686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -702,17 +702,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -725,17 +725,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -749,17 +749,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="11" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -854,7 +854,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -958,19 +958,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>57</v>
       </c>
@@ -996,7 +996,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>51</v>
       </c>
@@ -1030,13 +1030,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2386AE-B180-4489-BA71-14068DFEFD5A}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>69</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>73</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>74</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>75</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>76</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>77</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>78</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>79</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>80</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>81</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>82</v>
       </c>

--- a/TestData/TMTT0035971_VerifyOpportunityToEngagementConversionDefaultStartDateStatus.xlsx
+++ b/TestData/TMTT0035971_VerifyOpportunityToEngagementConversionDefaultStartDateStatus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE15B2F-0943-46E8-8D52-6223263FD786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FEAC03-079C-4C78-99B4-F6DB9AE448C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
@@ -86,9 +86,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -308,14 +305,17 @@
     <t>Verbally Engaged</t>
   </si>
   <si>
-    <t>Business Services</t>
+    <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>CSDN-0000007327</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,16 +331,211 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="20"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="52"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="23"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color indexed="54"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color indexed="54"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="54"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="62"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="52"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="60"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="63"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color indexed="54"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="27"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="26"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="31"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="44"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="49"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="53"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="51"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="62"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -348,9 +543,153 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="23"/>
+      </left>
+      <right style="thin">
+        <color indexed="23"/>
+      </right>
+      <top style="thin">
+        <color indexed="23"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="63"/>
+      </left>
+      <right style="double">
+        <color indexed="63"/>
+      </right>
+      <top style="double">
+        <color indexed="63"/>
+      </top>
+      <bottom style="double">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="49"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="44"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="44"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="52"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="22"/>
+      </left>
+      <right style="thin">
+        <color indexed="22"/>
+      </right>
+      <top style="thin">
+        <color indexed="22"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="63"/>
+      </left>
+      <right style="thin">
+        <color indexed="63"/>
+      </right>
+      <top style="thin">
+        <color indexed="63"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="49"/>
+      </top>
+      <bottom style="double">
+        <color indexed="49"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="2" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyFont="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyFont="0"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyFont="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -363,8 +702,50 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="43">
+    <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{5636E606-A66F-4C7B-A038-D0ADB18AD88A}"/>
+    <cellStyle name="20% - Accent2 2" xfId="7" xr:uid="{EE3C6F22-5781-437E-A686-0FFBB044A710}"/>
+    <cellStyle name="20% - Accent3 2" xfId="3" xr:uid="{B3E050D0-CBDC-442C-8E28-F48635836CFC}"/>
+    <cellStyle name="20% - Accent4 2" xfId="4" xr:uid="{088B526E-CEA9-41D0-A027-665C2F6BE72B}"/>
+    <cellStyle name="20% - Accent5 2" xfId="5" xr:uid="{E67CFD75-E01A-4AA9-ADF1-FE050CF9CB79}"/>
+    <cellStyle name="20% - Accent6 2" xfId="6" xr:uid="{00C64073-C239-429A-8369-BC372448DD89}"/>
+    <cellStyle name="40% - Accent1 2" xfId="9" xr:uid="{BF275268-EF52-4392-A758-3C3D30DA43D1}"/>
+    <cellStyle name="40% - Accent2 2" xfId="7" xr:uid="{4770C013-D224-4388-A8FD-64E80CCD4206}"/>
+    <cellStyle name="40% - Accent3 2" xfId="8" xr:uid="{4BE11BB0-11DD-4032-A0D0-1F274D7D2DF8}"/>
+    <cellStyle name="40% - Accent4 2" xfId="10" xr:uid="{EE4BDF2C-37F3-4456-A963-457339CB5182}"/>
+    <cellStyle name="40% - Accent5 2" xfId="9" xr:uid="{C7B62DE6-4347-49B4-81F9-C629887EE0E8}"/>
+    <cellStyle name="40% - Accent6 2" xfId="10" xr:uid="{C8ECD16A-E4FD-45FF-B923-F5F2E96F44D7}"/>
+    <cellStyle name="60% - Accent1 2" xfId="11" xr:uid="{F0F6B7A2-97FB-4F02-AEED-33E41F50E153}"/>
+    <cellStyle name="60% - Accent2 2" xfId="12" xr:uid="{50594FED-186C-4145-B516-C0D7449C267F}"/>
+    <cellStyle name="60% - Accent3 2" xfId="13" xr:uid="{6B79BCC9-A801-441C-8DBC-A2CC39546E45}"/>
+    <cellStyle name="60% - Accent4 2" xfId="14" xr:uid="{9F54B3BF-82BA-4176-A107-EB098E179F2F}"/>
+    <cellStyle name="60% - Accent5 2" xfId="15" xr:uid="{F2B1D1A5-E432-400D-9C8B-B517F71338EA}"/>
+    <cellStyle name="60% - Accent6 2" xfId="20" xr:uid="{D28385D6-5FDA-4C81-A8E1-5E9184EC9898}"/>
+    <cellStyle name="Accent1 2" xfId="15" xr:uid="{A5DDF0E1-B602-43E3-AB0D-5F16A0972FB8}"/>
+    <cellStyle name="Accent2 2" xfId="16" xr:uid="{951F215A-2A8B-419F-8870-11F474EDCB5B}"/>
+    <cellStyle name="Accent3 2" xfId="17" xr:uid="{E3D12DED-A47B-40E5-8A26-80EEB1F3D54C}"/>
+    <cellStyle name="Accent4 2" xfId="18" xr:uid="{E8BB5B97-C42A-4472-83A5-FBFC2A1CE17F}"/>
+    <cellStyle name="Accent5 2" xfId="19" xr:uid="{544B1932-7BFE-4714-8258-0D6ABF698F4E}"/>
+    <cellStyle name="Accent6 2" xfId="20" xr:uid="{9C52BCF0-4168-456D-BE4F-6FA76777F0F7}"/>
+    <cellStyle name="Bad 2" xfId="21" xr:uid="{F06B2E75-7994-4A52-B1BD-371C73C4C586}"/>
+    <cellStyle name="Calculation 2" xfId="22" xr:uid="{ED2EEC8E-521E-46D0-98E5-F9BF0C3A2959}"/>
+    <cellStyle name="Check Cell 2" xfId="23" xr:uid="{68C768F9-865E-4859-852D-D7E4AF9978A8}"/>
+    <cellStyle name="Explanatory Text 2" xfId="24" xr:uid="{492BDDBF-13BE-40F7-AA93-E61901223E73}"/>
+    <cellStyle name="Good 2" xfId="25" xr:uid="{6539E9BD-535E-41AD-9910-0F553C3FD5F1}"/>
+    <cellStyle name="Heading 1 2" xfId="26" xr:uid="{421FAF7E-BBBA-4F0F-A890-A6E607B82285}"/>
+    <cellStyle name="Heading 2 2" xfId="27" xr:uid="{B1FBD4A6-8917-409C-9140-65DD7BA5CF0F}"/>
+    <cellStyle name="Heading 3 2" xfId="28" xr:uid="{8618FD50-3F73-4A8F-87DE-6403E0430BB1}"/>
+    <cellStyle name="Heading 4 2" xfId="29" xr:uid="{DF0083E1-60D0-40D4-9F95-3CC44E433512}"/>
+    <cellStyle name="Input 2" xfId="30" xr:uid="{4AA59575-44F3-41DD-B7C5-6B4067675CC3}"/>
+    <cellStyle name="Linked Cell 2" xfId="31" xr:uid="{D0D51434-CBED-4B69-B1C2-8FD3938737A7}"/>
+    <cellStyle name="Neutral 2" xfId="32" xr:uid="{7ED431F3-0E29-4138-9590-A9A910FB1273}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{32AE6263-AFF2-4721-BBCA-86633C50D63D}"/>
+    <cellStyle name="Note 2" xfId="33" xr:uid="{AD926071-DD40-4772-932F-EBDCB8362644}"/>
+    <cellStyle name="Output 2" xfId="34" xr:uid="{5FF77F40-8553-46E8-81B3-6EF01632ECEA}"/>
+    <cellStyle name="Title 2" xfId="35" xr:uid="{DB4FC4E1-2F09-47B9-946B-50A3DC2EFBC2}"/>
+    <cellStyle name="Total 2" xfId="36" xr:uid="{D5F9A560-0215-4738-BFD2-F23C306AD528}"/>
+    <cellStyle name="Warning Text 2" xfId="37" xr:uid="{9799E486-8DA1-44C4-B120-E9A020E6895C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -659,7 +1040,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -770,183 +1151,183 @@
         <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AD1" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="AE1" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
         <v>88</v>
       </c>
       <c r="E2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" t="s">
         <v>42</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" t="s">
         <v>43</v>
       </c>
-      <c r="G2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L2" t="s">
         <v>44</v>
       </c>
-      <c r="I2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K2" t="s">
-        <v>84</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>45</v>
-      </c>
-      <c r="M2" t="s">
-        <v>46</v>
       </c>
       <c r="N2" t="s">
         <v>0</v>
       </c>
       <c r="O2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="R2" t="s">
         <v>47</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="S2" t="s">
         <v>47</v>
       </c>
-      <c r="Q2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="T2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" t="s">
         <v>49</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>50</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>51</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>52</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>53</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>54</v>
       </c>
-      <c r="Z2" t="s">
-        <v>55</v>
-      </c>
       <c r="AA2" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AC2" t="s">
         <v>0</v>
       </c>
       <c r="AD2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AE2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -972,54 +1353,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" t="s">
         <v>64</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>66</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1041,15 +1422,15 @@
         <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -1057,10 +1438,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" t="s">
         <v>69</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1068,10 +1449,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -1079,10 +1460,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1090,10 +1471,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1101,10 +1482,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1112,10 +1493,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1123,10 +1504,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1134,10 +1515,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1145,10 +1526,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1156,10 +1537,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1167,10 +1548,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1178,10 +1559,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>83</v>
       </c>
       <c r="C14">
         <v>13</v>

--- a/TestData/TMTT0035971_VerifyOpportunityToEngagementConversionDefaultStartDateStatus.xlsx
+++ b/TestData/TMTT0035971_VerifyOpportunityToEngagementConversionDefaultStartDateStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FEAC03-079C-4C78-99B4-F6DB9AE448C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95736C7D-792B-465C-9966-30C9B5800E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
@@ -308,7 +308,7 @@
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -691,7 +691,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -701,6 +701,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{5636E606-A66F-4C7B-A038-D0ADB18AD88A}"/>
@@ -1024,13 +1025,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1038,7 +1039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -1054,12 +1055,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FBB8EB1-471A-4668-845A-6810E22F6BA4}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1067,7 +1068,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1083,17 +1084,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1106,17 +1107,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1130,17 +1131,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="11" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -1235,14 +1237,14 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>40</v>
       </c>
       <c r="B2" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>73</v>
       </c>
       <c r="D2" t="s">
@@ -1339,19 +1341,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>56</v>
       </c>
@@ -1377,7 +1379,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>50</v>
       </c>
@@ -1411,13 +1413,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2386AE-B180-4489-BA71-14068DFEFD5A}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -1425,7 +1427,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -1436,7 +1438,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>68</v>
       </c>
@@ -1447,7 +1449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>70</v>
       </c>
@@ -1458,7 +1460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>72</v>
       </c>
@@ -1469,7 +1471,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>73</v>
       </c>
@@ -1480,7 +1482,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>74</v>
       </c>
@@ -1491,7 +1493,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>75</v>
       </c>
@@ -1502,7 +1504,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>76</v>
       </c>
@@ -1513,7 +1515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>77</v>
       </c>
@@ -1524,7 +1526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>78</v>
       </c>
@@ -1535,7 +1537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>79</v>
       </c>
@@ -1546,7 +1548,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>80</v>
       </c>
@@ -1557,7 +1559,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>81</v>
       </c>

--- a/TestData/TMTT0035971_VerifyOpportunityToEngagementConversionDefaultStartDateStatus.xlsx
+++ b/TestData/TMTT0035971_VerifyOpportunityToEngagementConversionDefaultStartDateStatus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95736C7D-792B-465C-9966-30C9B5800E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09790B6-DAA0-426F-8709-C17DA96B7DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <sheet name="ModuleName" sheetId="4" r:id="rId4"/>
     <sheet name="AddOpportunity" sheetId="12" r:id="rId5"/>
     <sheet name="AddContact" sheetId="14" r:id="rId6"/>
-    <sheet name="Engagement" sheetId="15" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="75">
   <si>
     <t>James Craven</t>
   </si>
@@ -248,49 +247,7 @@
     <t>Kristian M. Whalen</t>
   </si>
   <si>
-    <t>Lender Education</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>Buyside</t>
-  </si>
-  <si>
-    <t>Sellside</t>
-  </si>
-  <si>
-    <t>ESOP Corporate Finance</t>
-  </si>
-  <si>
     <t>General Financial Advisory</t>
-  </si>
-  <si>
-    <t>Real Estate Brokerage</t>
-  </si>
-  <si>
-    <t>Special Committee Advisory</t>
-  </si>
-  <si>
-    <t>Strategic Alternatives Study</t>
-  </si>
-  <si>
-    <t>Take Over Defense</t>
-  </si>
-  <si>
-    <t>Activism Advisory</t>
-  </si>
-  <si>
-    <t>Strategy</t>
-  </si>
-  <si>
-    <t>Post Merger Integration</t>
-  </si>
-  <si>
-    <t>Valuation Advisory</t>
-  </si>
-  <si>
-    <t>Advisory (CF)</t>
   </si>
   <si>
     <t>LA</t>
@@ -691,17 +648,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{5636E606-A66F-4C7B-A038-D0ADB18AD88A}"/>
@@ -1025,13 +978,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1039,9 +992,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -1055,12 +1008,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FBB8EB1-471A-4668-845A-6810E22F6BA4}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1068,7 +1021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1084,17 +1037,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1107,17 +1060,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1131,18 +1084,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="11" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -1153,7 +1106,7 @@
         <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>14</v>
@@ -1234,21 +1187,21 @@
         <v>39</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>40</v>
       </c>
       <c r="B2" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>73</v>
+      <c r="C2" t="s">
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
         <v>41</v>
@@ -1269,7 +1222,7 @@
         <v>42</v>
       </c>
       <c r="K2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="L2" t="s">
         <v>44</v>
@@ -1329,7 +1282,7 @@
         <v>55</v>
       </c>
       <c r="AE2" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1341,19 +1294,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>56</v>
       </c>
@@ -1379,7 +1332,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>50</v>
       </c>
@@ -1408,170 +1361,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2386AE-B180-4489-BA71-14068DFEFD5A}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/TestData/TMTT0035971_VerifyOpportunityToEngagementConversionDefaultStartDateStatus.xlsx
+++ b/TestData/TMTT0035971_VerifyOpportunityToEngagementConversionDefaultStartDateStatus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD730A2-003D-462E-B71F-84C229AC4AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6614F81-2668-4AD8-B478-9215CB29F066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
@@ -70,9 +70,6 @@
     <t>Type</t>
   </si>
   <si>
-    <t>Gemma Hardy</t>
-  </si>
-  <si>
     <t>CAO</t>
   </si>
   <si>
@@ -266,6 +263,9 @@
   </si>
   <si>
     <t>BUS - Business Services</t>
+  </si>
+  <si>
+    <t>Jennie Stewart</t>
   </si>
 </sst>
 </file>
@@ -648,14 +648,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{5636E606-A66F-4C7B-A038-D0ADB18AD88A}"/>
@@ -995,7 +994,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -1024,10 +1023,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1098,192 +1097,192 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AD1" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="AE1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" t="s">
         <v>40</v>
       </c>
-      <c r="B2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
         <v>43</v>
       </c>
-      <c r="I2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>44</v>
-      </c>
-      <c r="M2" t="s">
-        <v>45</v>
       </c>
       <c r="N2" t="s">
         <v>0</v>
       </c>
       <c r="O2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="R2" t="s">
         <v>46</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="S2" t="s">
         <v>46</v>
       </c>
-      <c r="Q2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="T2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="S2" t="s">
-        <v>47</v>
-      </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" t="s">
         <v>48</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>49</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>50</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>51</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>52</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>53</v>
       </c>
-      <c r="Z2" t="s">
-        <v>54</v>
-      </c>
       <c r="AA2" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AC2" t="s">
         <v>0</v>
       </c>
       <c r="AD2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AE2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1309,54 +1308,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
         <v>63</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>64</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
         <v>65</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTT0035971_VerifyOpportunityToEngagementConversionDefaultStartDateStatus.xlsx
+++ b/TestData/TMTT0035971_VerifyOpportunityToEngagementConversionDefaultStartDateStatus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6614F81-2668-4AD8-B478-9215CB29F066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8388FFF-993F-45B9-B5B1-15529FE7B850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
